--- a/output/pdf_financials_xlsx/RMB.xlsx
+++ b/output/pdf_financials_xlsx/RMB.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.114033</v>
+        <v>-0.114033</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.148686</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.114033</v>
+        <v>-0.114033</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>0.132437</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.114033</v>
+        <v>-0.114033</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0.132437</v>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.114033</v>
+        <v>-0.114033</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>0.148686</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.114033</v>
+        <v>-0.114033</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0.167263</v>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>13.53119997847813</v>
@@ -11544,7 +11544,7 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>0.114033</v>
+        <v>-0.114033</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -12118,10 +12118,10 @@
         </is>
       </c>
       <c r="E213" s="5" t="n">
-        <v>0.006054</v>
+        <v>-0.006054</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>0.114033</v>
+        <v>-0.114033</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RMB.xlsx
+++ b/output/pdf_financials_xlsx/RMB.xlsx
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.046485</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.051214</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.553096</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.209833</v>
       </c>
     </row>
     <row r="35">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.046485</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.051214</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.553096</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.209833</v>
       </c>
     </row>
     <row r="37">
@@ -1489,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.506642</v>
+        <v>0.455428</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.553096</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1.101347</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.614813</v>
+        <v>1.40498</v>
       </c>
     </row>
     <row r="49">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">

--- a/output/pdf_financials_xlsx/RMB.xlsx
+++ b/output/pdf_financials_xlsx/RMB.xlsx
@@ -1066,10 +1066,10 @@
         <v>0.017522</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.130632</v>
+        <v>0.037881</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.394876</v>
+        <v>0.109228</v>
       </c>
     </row>
     <row r="29">
@@ -1088,10 +1088,10 @@
         <v>-1.317408</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.491685</v>
+        <v>-0.584436</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.9878440000000001</v>
+        <v>0.702196</v>
       </c>
     </row>
     <row r="30">
@@ -1112,10 +1112,10 @@
         <v>-137.420241146337</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-19.40945609231556</v>
+        <v>-23.07083779405216</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>13.9385953067208</v>
+        <v>9.908068348846703</v>
       </c>
     </row>
     <row r="31">
@@ -2644,10 +2644,10 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.037881</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.109228</v>
       </c>
     </row>
     <row r="101">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">

--- a/output/pdf_financials_xlsx/RMB.xlsx
+++ b/output/pdf_financials_xlsx/RMB.xlsx
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.046485</v>
+        <v>0.391212</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.051214</v>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.046485</v>
+        <v>0.391212</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.051214</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>0.13</v>
+        <v>0.391212</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>1.21894</v>
@@ -1924,13 +1924,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.136307</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.357864</v>
       </c>
     </row>
     <row r="68">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.011054</v>
+        <v>0.023459</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.110025</v>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>0.011054</v>
+        <v>0.022459</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>0.784757</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0.125</v>
+        <v>0.400188</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.001</v>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.08765199999999999</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.08765199999999999</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>0.118946</v>
+        <v>0.367753</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>0.434183</v>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>0.118946</v>
+        <v>0.367753</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>0.434183</v>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>0.9149692307692308</v>
+        <v>0.9400350704988599</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>0.3561971877204784</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.057945</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.057945</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>0</v>
+        <v>-0.298242</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>0.041485</v>
+        <v>0.38841</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>-0.18382</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>0</v>
+        <v>0.046485</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.061627</v>
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>0.046485</v>
+        <v>0.391212</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.051214</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0.005</v>
+        <v>-0.043683</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>0.173407</v>
@@ -3441,7 +3441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I222"/>
+  <dimension ref="A1:I245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5514,26 +5514,20 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cash $</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
+          <t>As at June</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>0.046485</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0.391212</v>
+        <v>3e-05</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -5564,16 +5558,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Deferred financing costs</t>
+          <t>Cash $ 340,927 $</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DeferredFinancingCosts</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.025525</v>
+        <v>0.391212</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5609,12 +5603,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Subscription receivable</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Total assets $ 340,927 $</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
-        <v>0.05799</v>
+        <v>0.391212</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5650,19 +5648,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Total assets $</t>
+          <t>Accounts payable and accruals $ 19,505 $</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.391212</v>
+        <v>0.023459</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -5693,19 +5693,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Accounts payable and accruals $</t>
+          <t>Total liabilities 19,505</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.011054</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0.023459</v>
+        <v>0.022459</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -5731,24 +5733,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Share capital 4 400,188</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.011054</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0.023459</v>
+        <v>0.400188</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -5779,19 +5783,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Share capital 4</t>
+          <t>Contributed surplus 87,652</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>0.400188</v>
+        <v>0.08765199999999999</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5822,21 +5828,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0.08765199999999999</v>
+          <t>Deficit (166,418)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>-0.120087</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -5867,19 +5869,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Total shareholders’ equity 321,422</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>-0.006054</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>-0.120087</v>
+        <v>0.367753</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -5910,19 +5914,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity</t>
+          <t>Total liabilities and shareholders’ equity $ 340,927 $</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.118946</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0.367753</v>
+        <v>0.391212</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -5948,21 +5954,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shareholders' Equity</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders’ equity $</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.13</v>
+        <v>0.046485</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>0.391212</v>
@@ -5986,146 +5992,158 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0.132437</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-1.356078</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>-0.474046</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>0.545401</v>
+          <t>Deferred financing costs</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DeferredFinancingCosts</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0.025525</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.018577</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.017522</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>0.092751</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>0.285648</v>
+          <t>Subscription receivable</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>0.05799</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets</t>
+          <t>Total assets $</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.391212</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H64" s="5" t="n">
-        <v>0.037881</v>
-      </c>
-      <c r="I64" s="5" t="n">
-        <v>0.109228</v>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Amortization of right of use assets</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accruals $</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.011054</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.023459</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -6137,83 +6155,91 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="5" t="n">
-        <v>0.006846</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Provision for deferred tax</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DeferredTax</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.011054</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.00387</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>-0.027191</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>-0.162038</v>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>-0.1585</v>
+        <v>0.023459</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Write-off of related party balance</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital 4</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.400188</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="5" t="n">
-        <v>0.19</v>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -6224,22 +6250,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Stock base compensation</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6247,18 +6273,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F68" s="5" t="n">
+        <v>0.08765199999999999</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H68" s="5" t="n">
-        <v>0.122087</v>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -6269,29 +6295,29 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Interest on lease liability</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>-0.006054</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-0.120087</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -6303,86 +6329,96 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="5" t="n">
-        <v>0.0013</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gain on business combination</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total shareholders’ equity</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0.118946</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0.367753</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H70" s="5" t="n">
-        <v>-0.1553</v>
-      </c>
-      <c r="I70" s="5" t="n">
-        <v>-0.636884</v>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Accretion and accrued interest</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total liabilities and shareholders’ equity $</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.391212</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H71" s="5" t="n">
-        <v>0.077637</v>
-      </c>
-      <c r="I71" s="5" t="n">
-        <v>0.146306</v>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -6393,12 +6429,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Items not involving cash total</t>
+          <t>Net income (loss) and comprehensive income (loss)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -6408,16 +6444,16 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.173715</v>
+        <v>0.132437</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.09095300000000001</v>
+        <v>-1.356078</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>-0.271028</v>
+        <v>-0.474046</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>0.299345</v>
+        <v>0.545401</v>
       </c>
     </row>
     <row r="73">
@@ -6428,17 +6464,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6447,16 +6483,16 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.052058</v>
+        <v>0.018577</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.021126</v>
+        <v>0.017522</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.188084</v>
+        <v>0.092751</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.019267</v>
+        <v>0.285648</v>
       </c>
     </row>
     <row r="74">
@@ -6467,17 +6503,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Prepaids</t>
+          <t>Amortization of intangible assets</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6496,10 +6532,10 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>-0.002154</v>
+        <v>0.037881</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>-0.011275</v>
+        <v>0.109228</v>
       </c>
     </row>
     <row r="75">
@@ -6510,35 +6546,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>ChangeInInventory</t>
-        </is>
-      </c>
+          <t>Amortization of right of use assets</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F75" s="5" t="n">
-        <v>0.014814</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>-0.007098</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>0.004655</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I75" s="5" t="n">
-        <v>0.072203</v>
+        <v>0.006846</v>
       </c>
     </row>
     <row r="76">
@@ -6549,35 +6587,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Deposits</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Provision for deferred tax</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" s="5" t="n">
+        <v>-0.00387</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>-0.027191</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>0.013714</v>
+        <v>-0.162038</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>0.005417</v>
+        <v>-0.1585</v>
       </c>
     </row>
     <row r="77">
@@ -6588,12 +6626,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Write-off of related party balance</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6602,17 +6640,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F77" s="5" t="n">
-        <v>-0.010027</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.01219</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>-0.075569</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>0.002325</v>
+        <v>0.19</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -6623,17 +6667,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Stock base compensation</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6641,17 +6685,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" s="5" t="n">
-        <v>0.046963</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>0.02523</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0.122167</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>0.07187</v>
+        <v>0.122087</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -6662,35 +6712,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cash provided by operating activities</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Interest on lease liability</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>0.173407</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>0.142401</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>-0.020131</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I79" s="5" t="n">
-        <v>0.459152</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="80">
@@ -6701,19 +6753,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Purchase of property and equipment</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>PurchaseOfPPE</t>
-        </is>
-      </c>
+          <t>Gain on business combination</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -6724,14 +6772,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" s="5" t="n">
-        <v>-0.020749</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>-0.007929</v>
+        <v>-0.1553</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.006154</v>
+        <v>-0.636884</v>
       </c>
     </row>
     <row r="81">
@@ -6742,12 +6792,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cash paid for business combination (Note 5)</t>
+          <t>Accretion and accrued interest</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6767,10 +6817,10 @@
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>-4.006809</v>
+        <v>0.077637</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>-1.605</v>
+        <v>0.146306</v>
       </c>
     </row>
     <row r="82">
@@ -6781,12 +6831,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cash acquired on close of acquisition</t>
+          <t>Items not involving cash total</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6795,21 +6845,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F82" s="5" t="n">
+        <v>0.173715</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.09095300000000001</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>0.174591</v>
+        <v>-0.271028</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>0.042621</v>
+        <v>0.299345</v>
       </c>
     </row>
     <row r="83">
@@ -6820,17 +6866,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cash used in investing activities</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6838,21 +6884,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F83" s="5" t="n">
+        <v>-0.052058</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.021126</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>-3.840147</v>
+        <v>0.188084</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>-1.568533</v>
+        <v>0.019267</v>
       </c>
     </row>
     <row r="84">
@@ -6863,15 +6905,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Proceeds from option exercise</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>Prepaids</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -6888,10 +6934,10 @@
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>0.03945</v>
+        <v>-0.002154</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>0.00065</v>
+        <v>-0.011275</v>
       </c>
     </row>
     <row r="85">
@@ -6902,37 +6948,35 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Payment of lease liabilities</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F85" s="5" t="n">
+        <v>0.014814</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-0.007098</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0.004655</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>-0.007666</v>
+        <v>0.072203</v>
       </c>
     </row>
     <row r="86">
@@ -6943,12 +6987,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Increase in bank loan</t>
+          <t>Deposits</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6962,14 +7006,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G86" s="5" t="n">
-        <v>0.024303</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H86" s="5" t="n">
-        <v>3.535005</v>
+        <v>0.013714</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>3.582</v>
+        <v>0.005417</v>
       </c>
     </row>
     <row r="87">
@@ -6980,12 +7026,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Repayment of promissory note</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6994,21 +7040,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F87" s="5" t="n">
+        <v>-0.010027</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.01219</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>-0.25</v>
+        <v>-0.075569</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>-0.102</v>
+        <v>0.002325</v>
       </c>
     </row>
     <row r="88">
@@ -7019,37 +7061,35 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Proceeds from shareholder loans</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F88" s="5" t="n">
+        <v>0.046963</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.02523</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.122167</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>0.07187</v>
       </c>
     </row>
     <row r="89">
@@ -7060,37 +7100,35 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Repayment of shareholder loans</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Cash provided by operating activities</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" s="5" t="n">
+        <v>0.173407</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.142401</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>-0.020131</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>-0.1799</v>
+        <v>0.459152</v>
       </c>
     </row>
     <row r="90">
@@ -7101,15 +7139,19 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Repayment of bank loans</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Purchase of property and equipment</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -7120,16 +7162,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G90" s="5" t="n">
+        <v>-0.020749</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>-0.528199</v>
+        <v>-0.007929</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-1.917939</v>
+        <v>-0.006154</v>
       </c>
     </row>
     <row r="91">
@@ -7140,19 +7180,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Cash paid for business combination (Note 5)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -7169,10 +7205,10 @@
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>3.251251</v>
+        <v>-4.006809</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>1.375145</v>
+        <v>-1.605</v>
       </c>
     </row>
     <row r="92">
@@ -7183,35 +7219,35 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Cash acquired on close of acquisition</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>-0.010413</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>0.5018820000000001</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>-0.609027</v>
+        <v>0.174591</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.265764</v>
+        <v>0.042621</v>
       </c>
     </row>
     <row r="93">
@@ -7222,17 +7258,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
+          <t>Cash used in investing activities</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7240,17 +7276,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>0.061627</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>0.051214</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.553096</v>
+        <v>-3.840147</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-0.055931</v>
+        <v>-1.568533</v>
       </c>
     </row>
     <row r="94">
@@ -7266,30 +7306,30 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cash, end of the year</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Proceeds from option exercise</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>0.051214</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>0.553096</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>-0.055931</v>
+        <v>0.03945</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.209833</v>
+        <v>0.00065</v>
       </c>
     </row>
     <row r="95">
@@ -7300,12 +7340,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Write off of related party balance</t>
+          <t>Payment of lease liabilities</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -7324,13 +7364,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H95" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>-0.007666</v>
       </c>
     </row>
     <row r="96">
@@ -7341,12 +7381,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Gain on business combination                                                     (155,300)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Listing expenses</t>
+          <t>Increase in bank loan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -7361,17 +7401,13 @@
         </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1.373469</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.024303</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>3.535005</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>3.582</v>
       </c>
     </row>
     <row r="97">
@@ -7382,12 +7418,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Gain on business combination                                                     (155,300)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Accretion on promissory note</t>
+          <t>Repayment of promissory note</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7401,16 +7437,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G97" s="5" t="n">
-        <v>0.083231</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0.077637</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.25</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>-0.102</v>
       </c>
     </row>
     <row r="98">
@@ -7421,12 +7457,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Gain on business combination                                                     (155,300)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Gain on business combination                                                     (155,300) total</t>
+          <t>Proceeds from shareholder loans</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -7440,11 +7476,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G98" s="5" t="n">
-        <v>0.09095300000000001</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.271028</v>
+        <v>0.41</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7460,12 +7498,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cash acquired on close of reverse takeover</t>
+          <t>Repayment of shareholder loans</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -7479,18 +7517,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G99" s="5" t="n">
-        <v>0.324222</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="5" t="n">
+        <v>-0.1799</v>
       </c>
     </row>
     <row r="100">
@@ -7501,19 +7539,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cash provided by investing activities</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Repayment of bank loans</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -7524,16 +7558,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G100" s="5" t="n">
-        <v>0.303473</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-3.840147</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.528199</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>-1.917939</v>
       </c>
     </row>
     <row r="101">
@@ -7549,10 +7583,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Proceeds from private placement</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -7563,18 +7601,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G101" s="5" t="n">
-        <v>0.0565</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>3.251251</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>1.375145</v>
       </c>
     </row>
     <row r="102">
@@ -7590,12 +7626,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cash provided by (used in) financing activities</t>
+          <t>Increase (decrease) in cash</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7604,18 +7640,16 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.18382</v>
+        <v>-0.010413</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.056008</v>
+        <v>0.5018820000000001</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>3.251251</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.609027</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>0.265764</v>
       </c>
     </row>
     <row r="103">
@@ -7626,37 +7660,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Listing expenses</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="5" t="n">
+        <v>0.061627</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.373469</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.051214</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.553096</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>-0.055931</v>
       </c>
     </row>
     <row r="104">
@@ -7667,35 +7699,35 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Accretion on promissory note</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Cash, end of the year</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.026571</v>
+        <v>0.051214</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.083231</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.553096</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>-0.055931</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.209833</v>
       </c>
     </row>
     <row r="105">
@@ -7706,12 +7738,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Repayment of loans payable</t>
+          <t>Write off of related party balance</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -7720,16 +7752,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>-0.02382</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>-0.024795</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>0.19</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -7745,12 +7779,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Gain on business combination                                                     (155,300)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Proceeds from loans payable</t>
+          <t>Listing expenses</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -7765,7 +7799,7 @@
         </is>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.024303</v>
+        <v>1.373469</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7786,12 +7820,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Gain on business combination                                                     (155,300)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Advances to related parties</t>
+          <t>Accretion on promissory note</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -7800,18 +7834,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F107" s="5" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.083231</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>0.077637</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -7827,30 +7859,30 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>For the year     incorporation on</t>
+          <t>Gain on business combination                                                     (155,300)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>For the year     incorporation on ended June 30, February</t>
+          <t>Gain on business combination                                                     (155,300) total</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>2.5e-05</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.09095300000000001</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>-0.271028</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -7866,25 +7898,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>For the year     incorporation on</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Note 2022 to June</t>
+          <t>Cash acquired on close of reverse takeover</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.324222</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7905,34 +7939,34 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Cash provided by investing activities</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="n">
-        <v>-0.006054</v>
-      </c>
-      <c r="F110" s="5" t="n">
-        <v>-0.114033</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.303473</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>-3.840147</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -7948,17 +7982,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Proceeds from private placement</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7966,13 +8000,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F111" s="5" t="n">
-        <v>0.057945</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.0565</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7993,30 +8027,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Accounts payable and accruals</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" s="5" t="n">
-        <v>0.011054</v>
+          <t>Cash provided by (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.012405</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.18382</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.056008</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>3.251251</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -8032,29 +8068,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cash flows (used in) from operating activities</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>-0.043683</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Listing expenses</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>1.373469</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8075,25 +8109,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Proceeds from share issuance 4</t>
+          <t>Accretion on promissory note</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" s="5" t="n">
-        <v>0.125</v>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.026571</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.083231</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -8114,12 +8148,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Issuance costs</t>
+          <t>Repayment of loans payable</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -8129,12 +8163,10 @@
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>-0.095105</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.02382</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>-0.024795</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -8155,25 +8187,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Deferred financing costs</t>
+          <t>Proceeds from loans payable</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>-0.025525</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>0.025525</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.024303</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -8194,20 +8228,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Subscription receivable</t>
+          <t>Advances to related parties</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" s="5" t="n">
-        <v>-0.05799</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>0.05799</v>
+        <v>-0.16</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -8231,26 +8267,20 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Change in non-cash working capital items</t>
-        </is>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>For the years ended June</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" s="5" t="n">
-        <v>0.041485</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.38841</v>
+        <v>3e-05</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -8276,24 +8306,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Net loss and comprehensive loss $ (46,331) $</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" s="5" t="n">
-        <v>0.046485</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>0.344727</v>
+        <v>-0.114033</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -8319,26 +8347,26 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Share-based compensation -</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>0.046485</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.057945</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -8369,19 +8397,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Accounts payable and accruals (3,954)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" s="5" t="n">
-        <v>0.046485</v>
-      </c>
-      <c r="F121" s="5" t="n">
-        <v>0.391212</v>
+        <v>0.012405</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -8402,374 +8428,424 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Change in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Cash flows used in operating activities (50,285)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>0.862005</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>0.9586710000000001</v>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>2.533224</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>7.087113</v>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>-0.043683</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
+          <t>Proceeds from share issuance 4 -</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>0.298646</v>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>0.308441</v>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>0.899817</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>2.395013</v>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Cash flows from financing activities</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>0.5633590000000001</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>0.65023</v>
-      </c>
-      <c r="H124" s="5" t="n">
-        <v>1.633407</v>
-      </c>
-      <c r="I124" s="5" t="n">
-        <v>4.6921</v>
+          <t>Issuance costs -</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>-0.095105</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Deferred financing costs -</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" s="5" t="n">
-        <v>0.003054</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>0.310281</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>0.41226</v>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>0.582988</v>
-      </c>
-      <c r="I125" s="5" t="n">
-        <v>1.115714</v>
+        <v>0.025525</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Subscription receivable -</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>0.008214000000000001</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>0.08561100000000001</v>
-      </c>
-      <c r="H126" s="5" t="n">
-        <v>0.379345</v>
-      </c>
-      <c r="I126" s="5" t="n">
-        <v>0.447116</v>
+        <v>0.05799</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Cash flows from financing activities: -</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>0.38841</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G127" s="5" t="n">
-        <v>0.193401</v>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>0.707278</v>
-      </c>
-      <c r="I127" s="5" t="n">
-        <v>1.809001</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Management fees</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash (50,285)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" s="5" t="n">
+        <v>0.344727</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G128" s="5" t="n">
-        <v>0.0105</v>
-      </c>
-      <c r="H128" s="5" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="I128" s="5" t="n">
-        <v>0.18</v>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
+          <t>Cash, beginning of year 391,212</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>0.032047</v>
-      </c>
-      <c r="G129" s="5" t="n">
-        <v>0.000538</v>
-      </c>
-      <c r="H129" s="5" t="n">
-        <v>0.025377</v>
-      </c>
-      <c r="I129" s="5" t="n">
-        <v>0.043113</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0.046485</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Interest on loans</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year $ 340,927 $</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>0.391212</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G130" s="5" t="n">
-        <v>0.044672</v>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>0.153021</v>
-      </c>
-      <c r="I130" s="5" t="n">
-        <v>0.379602</v>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>For the year     incorporation on</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
+          <t>For the year     incorporation on ended June 30, February</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>2.5e-05</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H131" s="5" t="n">
-        <v>0.122087</v>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -8780,96 +8856,104 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>For the year     incorporation on</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Note 2022 to June</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" s="5" t="n">
+        <v>0.002021</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.018577</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>0.017522</v>
-      </c>
-      <c r="H132" s="5" t="n">
-        <v>0.092751</v>
-      </c>
-      <c r="I132" s="5" t="n">
-        <v>0.285648</v>
+        <v>3e-05</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>-0.006054</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.027197</v>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>0.01496</v>
-      </c>
-      <c r="H133" s="5" t="n">
-        <v>0.066659</v>
-      </c>
-      <c r="I133" s="5" t="n">
-        <v>0.195442</v>
+        <v>-0.114033</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8878,126 +8962,132 @@
         </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.388102</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>0.52846</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>2.295506</v>
-      </c>
-      <c r="I134" s="5" t="n">
-        <v>4.455636</v>
+        <v>0.057945</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Net income (loss) from operations</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accruals</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>0.011054</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>0.012405</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H135" s="5" t="n">
-        <v>-0.662099</v>
-      </c>
-      <c r="I135" s="5" t="n">
-        <v>0.236464</v>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Gain on business combination (Note 5)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash flows (used in) from operating activities</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>-0.043683</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H136" s="5" t="n">
-        <v>-0.1553</v>
-      </c>
-      <c r="I136" s="5" t="n">
-        <v>-0.636884</v>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Amortization of right of use asset (Note 8)</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from share issuance 4</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>0.4</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -9009,232 +9099,236 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="5" t="n">
-        <v>0.006846</v>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets (Note 9)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Issuance costs</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F138" s="5" t="n">
+        <v>-0.095105</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H138" s="5" t="n">
-        <v>0.037881</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>0.109228</v>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Accretion and accrued interest (Note 12,13)</t>
+          <t>Deferred financing costs</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E139" s="5" t="n">
+        <v>-0.025525</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>0.025525</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H139" s="5" t="n">
-        <v>0.077637</v>
-      </c>
-      <c r="I139" s="5" t="n">
-        <v>0.164306</v>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Net income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Subscription receivable</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" s="5" t="n">
+        <v>-0.05799</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>0.05799</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H140" s="5" t="n">
-        <v>-0.622317</v>
-      </c>
-      <c r="I140" s="5" t="n">
-        <v>0.5929680000000001</v>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Current income taxes</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="n">
-        <v>0.048339</v>
-      </c>
-      <c r="H141" s="5" t="n">
-        <v>0.013767</v>
-      </c>
-      <c r="I141" s="5" t="n">
-        <v>0.206067</v>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>0.041485</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (Note 14)</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="n">
-        <v>-0.027191</v>
-      </c>
-      <c r="H142" s="5" t="n">
-        <v>-0.162038</v>
-      </c>
-      <c r="I142" s="5" t="n">
-        <v>-0.1585</v>
+          <t>Increase in cash</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>0.046485</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>0.344727</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss)</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9242,60 +9336,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F143" s="5" t="n">
+        <v>0.046485</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H143" s="5" t="n">
-        <v>-0.474046</v>
-      </c>
-      <c r="I143" s="5" t="n">
-        <v>0.545401</v>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Equity holders of the Company</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>0.046485</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>0.391212</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H144" s="5" t="n">
-        <v>-0.463567</v>
-      </c>
-      <c r="I144" s="5" t="n">
-        <v>0.5566410000000001</v>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -9304,19 +9404,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9324,21 +9420,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F145" s="5" t="n">
+        <v>0.862005</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.9586710000000001</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>0.010479</v>
+        <v>2.533224</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>0.01124</v>
+        <v>7.087113</v>
       </c>
     </row>
     <row r="146">
@@ -9347,37 +9439,33 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Net Earnings per Common Share</t>
-        </is>
-      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F146" s="5" t="n">
+        <v>0.298646</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.308441</v>
       </c>
       <c r="H146" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.899817</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>2.395013</v>
       </c>
     </row>
     <row r="147">
@@ -9386,37 +9474,33 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Net Earnings per Common Share</t>
-        </is>
-      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F147" s="5" t="n">
+        <v>0.5633590000000001</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.65023</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>1.633407</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>5e-08</v>
+        <v>4.6921</v>
       </c>
     </row>
     <row r="148">
@@ -9427,39 +9511,33 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>0.003054</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>0.310281</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.41226</v>
       </c>
       <c r="H148" s="5" t="n">
-        <v>7.818527</v>
+        <v>0.582988</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>9.248182</v>
+        <v>1.115714</v>
       </c>
     </row>
     <row r="149">
@@ -9470,39 +9548,33 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Diluted</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>0.008214000000000001</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.08561100000000001</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>7.818527</v>
+        <v>0.379345</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>10.264631</v>
+        <v>0.447116</v>
       </c>
     </row>
     <row r="150">
@@ -9513,15 +9585,19 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 12,782,500 1,257,500 180,009 (922,895)</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>Salaries and benefits</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -9533,15 +9609,13 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.514614</v>
+        <v>0.193401</v>
       </c>
       <c r="H150" s="5" t="n">
-        <v>0.514614</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.707278</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>1.809001</v>
       </c>
     </row>
     <row r="151">
@@ -9552,15 +9626,19 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Exercise of agent’s options 393,500 78,008 (38,558) -</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>Management fees</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -9571,18 +9649,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G151" s="5" t="n">
+        <v>0.0105</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>0.03945</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.166</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="152">
@@ -9593,37 +9667,35 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Issuance of shareholder loan - - 127,480 -</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Interest and bank charges</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F152" s="5" t="n">
+        <v>0.032047</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.000538</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>0.12748</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025377</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>0.043113</v>
       </c>
     </row>
     <row r="153">
@@ -9634,12 +9706,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Share base compensation - -</t>
+          <t>Interest on loans</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -9653,16 +9725,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G153" s="5" t="n">
+        <v>0.044672</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>0.122087</v>
+        <v>0.153021</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>0.122087</v>
+        <v>0.379602</v>
       </c>
     </row>
     <row r="154">
@@ -9673,12 +9743,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - (463,567)</t>
+          <t>Share based compensation</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -9698,10 +9768,12 @@
         </is>
       </c>
       <c r="H154" s="5" t="n">
-        <v>-0.474046</v>
-      </c>
-      <c r="I154" s="5" t="n">
-        <v>-0.010479</v>
+        <v>0.122087</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -9712,33 +9784,35 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 13,176,000 1,335,508 391,018 (1,386,462)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F155" s="5" t="n">
+        <v>0.018577</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.329585</v>
+        <v>0.017522</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>0.329585</v>
+        <v>0.092751</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>-0.010479</v>
+        <v>0.285648</v>
       </c>
     </row>
     <row r="156">
@@ -9749,12 +9823,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Exercise of agent’s options 6,500 1,649 (999)</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -9763,23 +9837,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F156" s="5" t="n">
+        <v>0.027197</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.01496</v>
       </c>
       <c r="H156" s="5" t="n">
-        <v>0.00065</v>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.066659</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>0.195442</v>
       </c>
     </row>
     <row r="157">
@@ -9790,17 +9858,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income - - - 556,641</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9808,21 +9876,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F157" s="5" t="n">
+        <v>0.388102</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.52846</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>0.545401</v>
+        <v>2.295506</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>-0.01124</v>
+        <v>4.455636</v>
       </c>
     </row>
     <row r="158">
@@ -9833,15 +9897,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2025 13,182,500 1,337,157 390,019 (829,821)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>Net income (loss) from operations</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -9858,10 +9926,10 @@
         </is>
       </c>
       <c r="H158" s="5" t="n">
-        <v>0.875636</v>
+        <v>-0.662099</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>-0.021719</v>
+        <v>0.236464</v>
       </c>
     </row>
     <row r="159">
@@ -9872,19 +9940,15 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>General and administrative (Note 15)</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Gain on business combination (Note 5)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -9895,16 +9959,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G159" s="5" t="n">
-        <v>0.161256</v>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H159" s="5" t="n">
-        <v>0.582988</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.1553</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>-0.636884</v>
       </c>
     </row>
     <row r="160">
@@ -9920,7 +9984,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Gain on business combination</t>
+          <t>Amortization of right of use asset (Note 8)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -9939,13 +10003,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H160" s="5" t="n">
-        <v>-0.1553</v>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>0.006846</v>
       </c>
     </row>
     <row r="161">
@@ -9961,7 +10025,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets</t>
+          <t>Amortization of intangible assets (Note 9)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9987,10 +10051,8 @@
       <c r="H161" s="5" t="n">
         <v>0.037881</v>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I161" s="5" t="n">
+        <v>0.109228</v>
       </c>
     </row>
     <row r="162">
@@ -10006,7 +10068,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Listing expenses (Note 6)</t>
+          <t>Accretion and accrued interest (Note 12,13)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -10020,18 +10082,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G162" s="5" t="n">
-        <v>1.373469</v>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>0.077637</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>0.164306</v>
       </c>
     </row>
     <row r="163">
@@ -10047,10 +10107,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Accretion on promissory note (Note 12)</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Net income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -10061,16 +10125,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G163" s="5" t="n">
-        <v>0.083231</v>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H163" s="5" t="n">
-        <v>0.077637</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.622317</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>0.5929680000000001</v>
       </c>
     </row>
     <row r="164">
@@ -10086,12 +10150,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Net loss before income taxes</t>
+          <t>Current income taxes</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10105,15 +10169,13 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>-1.33493</v>
+        <v>0.048339</v>
       </c>
       <c r="H164" s="5" t="n">
-        <v>-0.622317</v>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013767</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>0.206067</v>
       </c>
     </row>
     <row r="165">
@@ -10129,12 +10191,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Deferred income tax recovery (Note 14)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10148,15 +10210,13 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>-1.356078</v>
+        <v>-0.027191</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>-0.474046</v>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.162038</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>-0.1585</v>
       </c>
     </row>
     <row r="166">
@@ -10167,15 +10227,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss attributable to</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Equity holders of the Company</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Net income (loss) and comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -10186,16 +10250,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G166" s="5" t="n">
-        <v>-1.356078</v>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H166" s="5" t="n">
-        <v>-0.463567</v>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.474046</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>0.545401</v>
       </c>
     </row>
     <row r="167">
@@ -10206,19 +10270,15 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss attributable to</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Equity holders of the Company</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -10235,12 +10295,10 @@
         </is>
       </c>
       <c r="H167" s="5" t="n">
-        <v>0.010479</v>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.463567</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>0.5566410000000001</v>
       </c>
     </row>
     <row r="168">
@@ -10251,17 +10309,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss attributable to</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Non-controlling interest</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>MinorityInterests</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10274,16 +10332,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G168" s="5" t="n">
-        <v>-1.356078</v>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H168" s="5" t="n">
-        <v>-0.474046</v>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010479</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>0.01124</v>
       </c>
     </row>
     <row r="169">
@@ -10294,19 +10352,15 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss attributable to</t>
+          <t>Net Earnings per Common Share</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (Note 16)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -10317,16 +10371,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G169" s="5" t="n">
-        <v>7.021836</v>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H169" s="5" t="n">
-        <v>7.818527</v>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>5.999999999999999e-08</v>
       </c>
     </row>
     <row r="170">
@@ -10337,12 +10391,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Net Earnings per Common Share</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 * 6,000,000 1,000 - 433,183</t>
+          <t>Diluted</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -10356,18 +10410,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G170" s="5" t="n">
-        <v>0.434183</v>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>5e-08</v>
       </c>
     </row>
     <row r="171">
@@ -10378,15 +10430,19 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Reverse takeover (note 6) 6,500,000 1,200,000 180,009 -</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -10397,18 +10453,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G171" s="5" t="n">
-        <v>1.380009</v>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>7.818527</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>9.248182</v>
       </c>
     </row>
     <row r="172">
@@ -10419,15 +10473,19 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Private placement 282,500 56,500 - -</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -10438,18 +10496,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G172" s="5" t="n">
-        <v>0.0565</v>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>7.818527</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>10.264631</v>
       </c>
     </row>
     <row r="173">
@@ -10465,7 +10521,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - (1,356,078)</t>
+          <t>Balance, December 31, 2023 12,782,500 1,257,500 180,009 (922,895)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -10480,12 +10536,10 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>-1.356078</v>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.514614</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>0.514614</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -10506,7 +10560,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Exercise of Agent’s options 393,500 78,008 (38,558)</t>
+          <t>Exercise of agent’s options 393,500 78,008 (38,558) -</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -10520,13 +10574,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G174" s="5" t="n">
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="n">
         <v>0.03945</v>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -10547,7 +10601,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Issuance of shareholder loan 127,480</t>
+          <t>Issuance of shareholder loan - - 127,480 -</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -10561,13 +10615,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G175" s="5" t="n">
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="n">
         <v>0.12748</v>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -10588,7 +10642,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Share base compensation 122,087</t>
+          <t>Share base compensation - -</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -10602,18 +10656,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G176" s="5" t="n">
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="n">
         <v>0.122087</v>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I176" s="5" t="n">
+        <v>0.122087</v>
       </c>
     </row>
     <row r="177">
@@ -10629,7 +10681,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - (629,155)</t>
+          <t>Net loss and comprehensive loss - - - (463,567)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -10643,16 +10695,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G177" s="5" t="n">
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="n">
         <v>-0.474046</v>
       </c>
-      <c r="H177" s="5" t="n">
+      <c r="I177" s="5" t="n">
         <v>-0.010479</v>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="178">
@@ -10663,19 +10715,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2024 13,176,000 1,335,508 391,018 (1,386,462)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -10687,17 +10735,13 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.020772</v>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.329585</v>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>0.329585</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>-0.010479</v>
       </c>
     </row>
     <row r="179">
@@ -10708,12 +10752,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Transaction costs</t>
+          <t>Exercise of agent’s options 6,500 1,649 (999)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -10727,13 +10771,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G179" s="5" t="n">
-        <v>0.017736</v>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>0.00065</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -10749,15 +10793,19 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Listing expenses (Note 5)</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Net income and comprehensive income - - - 556,641</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -10768,18 +10816,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G180" s="5" t="n">
-        <v>1.373469</v>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>0.545401</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>-0.01124</v>
       </c>
     </row>
     <row r="181">
@@ -10790,12 +10836,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Accretion on promissory note (Note 10)</t>
+          <t>Balance, December 31, 2025 13,182,500 1,337,157 390,019 (829,821)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -10804,21 +10850,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F181" s="5" t="n">
-        <v>0.026571</v>
-      </c>
-      <c r="G181" s="5" t="n">
-        <v>0.083231</v>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>0.875636</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>-0.021719</v>
       </c>
     </row>
     <row r="182">
@@ -10829,17 +10875,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Net (loss) income and comprehensive (loss) income before taxes</t>
+          <t>General and administrative (Note 15)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10847,16 +10893,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F182" s="5" t="n">
-        <v>0.148686</v>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>-1.33493</v>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.161256</v>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>0.582988</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -10877,29 +10923,27 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Current income taxes (Note 11)</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Gain on business combination</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F183" s="5" t="n">
-        <v>0.020119</v>
-      </c>
-      <c r="G183" s="5" t="n">
-        <v>0.048339</v>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>-0.1553</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -10920,25 +10964,31 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (Note 11)</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Amortization of intangible assets</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F184" s="5" t="n">
-        <v>-0.00387</v>
-      </c>
-      <c r="G184" s="5" t="n">
-        <v>-0.027191</v>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>0.037881</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -10959,7 +11009,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Net (loss) income and comprehensive (loss) income</t>
+          <t>Listing expenses (Note 6)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -10968,11 +11018,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F185" s="5" t="n">
-        <v>0.132437</v>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>-1.356078</v>
+        <v>1.373469</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -10998,29 +11050,25 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (Note 13)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Accretion on promissory note (Note 12)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F186" s="5" t="n">
-        <v>6</v>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>7.021836</v>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.083231</v>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>0.077637</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -11036,30 +11084,34 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Balance, January 1, 2022 * 6,000,000 1,000 -</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>Net loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F187" s="5" t="n">
-        <v>0.301746</v>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>0.300746</v>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.33493</v>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>-0.622317</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -11075,12 +11127,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Net income and comprehensive</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income - -</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11093,16 +11145,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F188" s="5" t="n">
-        <v>0.132437</v>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>0.132437</v>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.356078</v>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>-0.474046</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -11118,12 +11170,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Net income and comprehensive</t>
+          <t>Net loss and comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022* 6,000,000 1,000 -</t>
+          <t>Equity holders of the Company</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -11132,16 +11184,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F189" s="5" t="n">
-        <v>0.434183</v>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.433183</v>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.356078</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>-0.463567</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -11157,32 +11209,36 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Net income and comprehensive</t>
+          <t>Net loss and comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Reverse takeover (note 6) 6,500,000 1,200,000 180,009</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F190" s="5" t="n">
-        <v>1.380009</v>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H190" s="5" t="n">
+        <v>0.010479</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -11198,32 +11254,34 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Net income and comprehensive</t>
+          <t>Net loss and comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Private placement 282,500 56,500 -</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F191" s="5" t="n">
-        <v>0.0565</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>-1.356078</v>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>-0.474046</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -11239,17 +11297,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Net income and comprehensive</t>
+          <t>Net loss and comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - -</t>
+          <t>Weighted average number of common shares outstanding (Note 16)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11257,16 +11315,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F192" s="5" t="n">
-        <v>-1.356078</v>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>-1.356078</v>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.021836</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>7.818527</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -11282,12 +11340,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Net income and comprehensive</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 12,782,500 1,257,500 180,009</t>
+          <t>Balance, December 31, 2022 * 6,000,000 1,000 - 433,183</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -11296,11 +11354,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F193" s="5" t="n">
-        <v>0.514614</v>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>-0.922895</v>
+        <v>0.434183</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -11319,25 +11379,29 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>For the years ended June</t>
+          <t>Reverse takeover (note 6) 6,500,000 1,200,000 180,009 -</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" s="5" t="n">
-        <v>3e-05</v>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G194" s="5" t="n">
+        <v>1.380009</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -11358,27 +11422,27 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Share-based compensation -</t>
+          <t>Private placement 282,500 56,500 - -</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" s="5" t="n">
-        <v>0.057945</v>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G195" s="5" t="n">
+        <v>0.0565</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -11399,27 +11463,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Regulatory filing fees $ 22,998 $</t>
+          <t>Net loss and comprehensive loss - - - (1,356,078)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" s="5" t="n">
-        <v>0.033962</v>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G196" s="5" t="n">
+        <v>-1.356078</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -11440,31 +11504,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>General and administrative 13,025</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E197" s="5" t="n">
-        <v>0.013912</v>
+          <t>Exercise of Agent’s options 393,500 78,008 (38,558)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G197" s="5" t="n">
+        <v>0.03945</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -11485,31 +11545,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Professional fees 10,308</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E198" s="5" t="n">
-        <v>0.008214000000000001</v>
+          <t>Issuance of shareholder loan 127,480</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G198" s="5" t="n">
+        <v>0.12748</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -11530,31 +11586,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $ 46,331 $</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E199" s="5" t="n">
-        <v>-0.114033</v>
+          <t>Share base compensation 122,087</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G199" s="5" t="n">
+        <v>0.122087</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -11575,32 +11627,30 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share 6 $ (0.01) $</t>
+          <t>Net loss and comprehensive loss - - - (629,155)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
-      <c r="E200" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G200" s="5" t="n">
+        <v>-0.474046</v>
+      </c>
+      <c r="H200" s="5" t="n">
+        <v>-0.010479</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -11616,27 +11666,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2021 125,000 - (6,054)</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" s="5" t="n">
-        <v>0.118946</v>
+          <t>Regulatory fees</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G201" s="5" t="n">
+        <v>0.020772</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -11657,27 +11711,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Issuance of common shares 4 400,000 - -</t>
+          <t>Transaction costs</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
-      <c r="E202" s="5" t="n">
-        <v>0.4</v>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G202" s="5" t="n">
+        <v>0.017736</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -11698,27 +11752,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Share-based compensation - 87,652 -</t>
+          <t>Listing expenses (Note 5)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" s="5" t="n">
-        <v>0.08765199999999999</v>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G203" s="5" t="n">
+        <v>1.373469</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -11739,27 +11793,25 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Share issue costs (124,812) - -</t>
+          <t>Accretion on promissory note (Note 10)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
-      <c r="E204" s="5" t="n">
-        <v>-0.124812</v>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>0.026571</v>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>0.083231</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -11780,27 +11832,29 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - (114,033)</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" s="5" t="n">
-        <v>-0.114033</v>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net (loss) income and comprehensive (loss) income before taxes</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>0.148686</v>
+      </c>
+      <c r="G205" s="5" t="n">
+        <v>-1.33493</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -11821,27 +11875,29 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Balance at June 30, 2022 400,188 87,652 (120,087)</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" s="5" t="n">
-        <v>0.367753</v>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Current income taxes (Note 11)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>0.020119</v>
+      </c>
+      <c r="G206" s="5" t="n">
+        <v>0.048339</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -11862,27 +11918,29 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - (46,331)</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" s="5" t="n">
-        <v>-0.046331</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred income tax recovery (Note 11)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="n">
+        <v>-0.00387</v>
+      </c>
+      <c r="G207" s="5" t="n">
+        <v>-0.027191</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -11903,27 +11961,25 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Note             ($)               ($)             ($)                ($)</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Balance at June 30, 2023 400,188 87,652 (166,418)</t>
+          <t>Net (loss) income and comprehensive (loss) income</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" s="5" t="n">
-        <v>0.321422</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>0.132437</v>
+      </c>
+      <c r="G208" s="5" t="n">
+        <v>-1.356078</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -11944,25 +12000,29 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>For the year     incorporation on</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>For the year     incorporation on ended June 30, February</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" s="5" t="n">
-        <v>0.002021</v>
+          <t>Weighted average number of common shares outstanding (Note 13)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F209" s="5" t="n">
-        <v>2.5e-05</v>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="G209" s="5" t="n">
+        <v>7.021836</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -11983,25 +12043,25 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>For the year     incorporation on</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Note 2022 to June</t>
+          <t>Balance, January 1, 2022 * 6,000,000 1,000 -</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
-      <c r="E210" s="5" t="n">
-        <v>0.002021</v>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F210" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.301746</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>0.300746</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -12022,27 +12082,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income and comprehensive</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Share-based compensation $</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
+          <t>Net income and comprehensive income - -</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F211" s="5" t="n">
-        <v>0.057945</v>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.132437</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>0.132437</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -12063,12 +12125,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income and comprehensive</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Regulatory filing fees</t>
+          <t>Balance, December 31, 2022* 6,000,000 1,000 -</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -12078,12 +12140,10 @@
         </is>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.033962</v>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.434183</v>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>0.433183</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -12104,24 +12164,22 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income and comprehensive</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E213" s="5" t="n">
-        <v>-0.006054</v>
+          <t>Reverse takeover (note 6) 6,500,000 1,200,000 180,009</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F213" s="5" t="n">
-        <v>-0.114033</v>
+        <v>1.380009</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -12147,24 +12205,22 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income and comprehensive</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share 6 $</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="n">
-        <v>0</v>
+          <t>Private placement 282,500 56,500 -</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F214" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.0565</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -12190,29 +12246,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>At incorporation, February 25,</t>
+          <t>Net income and comprehensive</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>At incorporation, February 25,</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F215" s="5" t="n">
+        <v>-1.356078</v>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>-1.356078</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -12233,27 +12289,25 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>At incorporation, February 25,</t>
+          <t>Net income and comprehensive</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Issuance of common shares 4 125,000 -</t>
+          <t>Balance, December 31, 2023 12,782,500 1,257,500 180,009</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" s="5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>0.514614</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>-0.922895</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -12272,26 +12326,20 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>At incorporation, February 25,</t>
-        </is>
-      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - -</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>For the years ended June</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" s="5" t="n">
-        <v>-0.006054</v>
-      </c>
-      <c r="F217" s="5" t="n">
-        <v>-0.006054</v>
+        <v>3e-05</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -12317,20 +12365,22 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>At incorporation, February 25,</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Balance at June 30, 2021 125,000 -</t>
+          <t>Share-based compensation -</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" s="5" t="n">
-        <v>0.118946</v>
-      </c>
-      <c r="F218" s="5" t="n">
-        <v>-0.006054</v>
+        <v>0.057945</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -12356,17 +12406,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>At incorporation, February 25,</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Issuance of common shares 4 400,000 -</t>
+          <t>Regulatory filing fees $ 22,998 $</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" s="5" t="n">
-        <v>0.4</v>
+        <v>0.033962</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -12397,17 +12447,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>At incorporation, February 25,</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Share-based compensation - 87,652</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
+          <t>General and administrative 13,025</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E220" s="5" t="n">
-        <v>0.08765199999999999</v>
+        <v>0.013912</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -12438,17 +12492,21 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>At incorporation, February 25,</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Share issue costs (124,812) -</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>Professional fees 10,308</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E221" s="5" t="n">
-        <v>-0.124812</v>
+        <v>0.008214000000000001</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -12479,32 +12537,981 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss $ 46,331 $</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="n">
+        <v>-0.114033</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share 6 $ (0.01) $</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2021 125,000 - (6,054)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" s="5" t="n">
+        <v>0.118946</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Issuance of common shares 4 400,000 - -</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Share-based compensation - 87,652 -</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" s="5" t="n">
+        <v>0.08765199999999999</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Share issue costs (124,812) - -</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" s="5" t="n">
+        <v>-0.124812</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - (114,033)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" s="5" t="n">
+        <v>-0.114033</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Balance at June 30, 2022 400,188 87,652 (120,087)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" s="5" t="n">
+        <v>0.367753</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - (46,331)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" s="5" t="n">
+        <v>-0.046331</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Note             ($)               ($)             ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Balance at June 30, 2023 400,188 87,652 (166,418)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" s="5" t="n">
+        <v>0.321422</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>For the year     incorporation on</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>For the year     incorporation on ended June 30, February</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>2.5e-05</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>For the year     incorporation on</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Note 2022 to June</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F233" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Share-based compensation $</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>0.057945</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Regulatory filing fees</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>0.033962</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="n">
+        <v>-0.006054</v>
+      </c>
+      <c r="F236" s="5" t="n">
+        <v>-0.114033</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share 6 $</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
           <t>At incorporation, February 25,</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>At incorporation, February 25,</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>At incorporation, February 25,</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Issuance of common shares 4 125,000 -</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>At incorporation, February 25,</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - -</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E240" s="5" t="n">
+        <v>-0.006054</v>
+      </c>
+      <c r="F240" s="5" t="n">
+        <v>-0.006054</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>At incorporation, February 25,</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Balance at June 30, 2021 125,000 -</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" s="5" t="n">
+        <v>0.118946</v>
+      </c>
+      <c r="F241" s="5" t="n">
+        <v>-0.006054</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>At incorporation, February 25,</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Issuance of common shares 4 400,000 -</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>At incorporation, February 25,</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Share-based compensation - 87,652</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" s="5" t="n">
+        <v>0.08765199999999999</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>At incorporation, February 25,</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Share issue costs (124,812) -</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" s="5" t="n">
+        <v>-0.124812</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>At incorporation, February 25,</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
         <is>
           <t>Balance at June 30, 2022 400,188 87,652</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" s="5" t="n">
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" s="5" t="n">
         <v>0.367753</v>
       </c>
-      <c r="F222" s="5" t="n">
+      <c r="F245" s="5" t="n">
         <v>-0.120087</v>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
         <is>
           <t>-</t>
         </is>
